--- a/TP2/Tabla.xlsx
+++ b/TP2/Tabla.xlsx
@@ -13,11 +13,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={473f2be6-bf37-4d6c-aadd-985685d0a223}</author>
-    <author>tc={e4642d32-e35a-4aff-9331-18783ec953c4}</author>
+    <author>tc={15691d26-e45d-4ffe-812f-86b8d0998af2}</author>
+    <author>tc={2509df73-bc59-42ee-b9f3-c18b2b00ef66}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{473f2be6-bf37-4d6c-aadd-985685d0a223}" ref="E10">
+    <comment authorId="0" xr:uid="{15691d26-e45d-4ffe-812f-86b8d0998af2}" ref="E10">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -26,7 +26,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{e4642d32-e35a-4aff-9331-18783ec953c4}" ref="E9">
+    <comment authorId="1" xr:uid="{2509df73-bc59-42ee-b9f3-c18b2b00ef66}" ref="E9">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="52">
   <si>
     <t>TT</t>
   </si>
@@ -196,28 +196,13 @@
   </si>
   <si>
     <t xml:space="preserve">Se detectó un / y se debe determinar si correponde a una división o un /= </t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>"+"</t>
-  </si>
-  <si>
-    <t>100+</t>
-  </si>
-  <si>
-    <t>... (102+ a 112+)</t>
-  </si>
-  <si>
-    <t>999+ (Error)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -228,15 +213,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF1F1F1F"/>
-      <name val="&quot;Google Sans Text&quot;"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1F1F1F"/>
-      <name val="&quot;Google Sans Text&quot;"/>
     </font>
   </fonts>
   <fills count="2">
@@ -447,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -510,13 +486,6 @@
     </xf>
     <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,7 +505,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Matias Bisceglia" id="{0d341574-78e1-431a-963e-a2616729d9e8}" providerId="google-sheets"/>
+  <x18tc:person displayName="Matias Bisceglia" id="{2e6a1d2f-af35-41e7-b9eb-59f3e11e140c}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -736,10 +705,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E9" dT="2026-09-12T15:13:46.00" personId="{0d341574-78e1-431a-963e-a2616729d9e8}" id="{e4642d32-e35a-4aff-9331-18783ec953c4}" done="1">
+  <x18tc:threadedComment ref="E9" dT="2026-09-12T15:13:46.00" personId="{2e6a1d2f-af35-41e7-b9eb-59f3e11e140c}" id="{2509df73-bc59-42ee-b9f3-c18b2b00ef66}" done="1">
     <x18tc:text xml:space="preserve">En mi calculadora al poner un numero, un punto y una variable lo toma como una multiplicación. Podríamos usar ese enfoque o simplemente decir que es un error</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E10" dT="2026-09-12T15:25:15.00" personId="{0d341574-78e1-431a-963e-a2616729d9e8}" id="{473f2be6-bf37-4d6c-aadd-985685d0a223}" done="1">
+  <x18tc:threadedComment ref="E10" dT="2026-09-12T15:25:15.00" personId="{2e6a1d2f-af35-41e7-b9eb-59f3e11e140c}" id="{15691d26-e45d-4ffe-812f-86b8d0998af2}" done="1">
     <x18tc:text xml:space="preserve">Mismo que el de arriba, pero considera el primer dígito un 0</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1842,591 +1811,16 @@
         <v>51</v>
       </c>
     </row>
-    <row r="65">
-      <c r="E65" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F65" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="H65" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="I65" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="J65" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="K65" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="L65" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="M65" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="N65" s="22" t="str">
-        <f/>
-        <v>#ERROR!</v>
-      </c>
-      <c r="O65" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="P65" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q65" s="21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="E66" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="21">
-        <v>1.0</v>
-      </c>
-      <c r="G66" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="H66" s="21">
-        <v>4.0</v>
-      </c>
-      <c r="I66" s="21">
-        <v>5.0</v>
-      </c>
-      <c r="J66" s="21">
-        <v>6.0</v>
-      </c>
-      <c r="K66" s="21">
-        <v>7.0</v>
-      </c>
-      <c r="L66" s="21">
-        <v>8.0</v>
-      </c>
-      <c r="M66" s="21">
-        <v>110.0</v>
-      </c>
-      <c r="N66" s="21">
-        <v>111.0</v>
-      </c>
-      <c r="O66" s="21">
-        <v>112.0</v>
-      </c>
-      <c r="P66" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="Q66" s="21">
-        <v>999.0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="E67" s="23">
-        <v>1.0</v>
-      </c>
-      <c r="F67" s="21">
-        <v>1.0</v>
-      </c>
-      <c r="G67" s="21">
-        <v>1.0</v>
-      </c>
-      <c r="H67" s="21">
-        <v>100.0</v>
-      </c>
-      <c r="I67" s="21">
-        <v>100.0</v>
-      </c>
-      <c r="J67" s="21">
-        <v>100.0</v>
-      </c>
-      <c r="K67" s="21">
-        <v>100.0</v>
-      </c>
-      <c r="L67" s="21">
-        <v>100.0</v>
-      </c>
-      <c r="M67" s="21">
-        <v>100.0</v>
-      </c>
-      <c r="N67" s="21">
-        <v>100.0</v>
-      </c>
-      <c r="O67" s="21">
-        <v>100.0</v>
-      </c>
-      <c r="P67" s="21">
-        <v>100.0</v>
-      </c>
-      <c r="Q67" s="21">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="E68" s="23">
-        <v>2.0</v>
-      </c>
-      <c r="F68" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="G68" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="H68" s="21">
-        <v>3.0</v>
-      </c>
-      <c r="I68" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="J68" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="K68" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="L68" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="M68" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="N68" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="O68" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="P68" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="Q68" s="21">
-        <v>101.0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="E69" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="F69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="G69" s="21">
-        <v>3.0</v>
-      </c>
-      <c r="H69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="I69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="J69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="K69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="L69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="M69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="N69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="O69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="P69" s="21">
-        <v>101.0</v>
-      </c>
-      <c r="Q69" s="21">
-        <v>101.0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="E70" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="F70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="G70" s="21">
-        <v>3.0</v>
-      </c>
-      <c r="H70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="I70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="J70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="K70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="L70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="M70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="N70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="O70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="P70" s="21">
-        <v>999.0</v>
-      </c>
-      <c r="Q70" s="21">
-        <v>999.0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="E71" s="23">
-        <v>5.0</v>
-      </c>
-      <c r="F71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="G71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="H71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="I71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="J71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="K71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="L71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="M71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="N71" s="21">
-        <v>103.0</v>
-      </c>
-      <c r="O71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="P71" s="21">
-        <v>102.0</v>
-      </c>
-      <c r="Q71" s="21">
-        <v>102.0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="E72" s="23">
-        <v>6.0</v>
-      </c>
-      <c r="F72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="G72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="H72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="I72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="J72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="K72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="L72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="M72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="N72" s="21">
-        <v>105.0</v>
-      </c>
-      <c r="O72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="P72" s="21">
-        <v>104.0</v>
-      </c>
-      <c r="Q72" s="21">
-        <v>104.0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="E73" s="23">
-        <v>7.0</v>
-      </c>
-      <c r="F73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="G73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="H73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="I73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="J73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="K73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="L73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="M73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="N73" s="21">
-        <v>107.0</v>
-      </c>
-      <c r="O73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="P73" s="21">
-        <v>106.0</v>
-      </c>
-      <c r="Q73" s="21">
-        <v>106.0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="E74" s="23">
-        <v>8.0</v>
-      </c>
-      <c r="F74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="G74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="H74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="I74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="J74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="K74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="L74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="M74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="N74" s="21">
-        <v>109.0</v>
-      </c>
-      <c r="O74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="P74" s="21">
-        <v>108.0</v>
-      </c>
-      <c r="Q74" s="21">
-        <v>108.0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="E75" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="F75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="H75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="I75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="J75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="K75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="L75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="M75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="N75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="O75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="P75" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q75" s="21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="E76" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="H76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="I76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="J76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="K76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="L76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="M76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="N76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="O76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="P76" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q76" s="21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="E77" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="H77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="I77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="J77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="K77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="L77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="M77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="N77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="O77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="P77" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q77" s="21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="E78" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="F78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="H78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="I78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="J78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="K78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="L78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="M78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="N78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="O78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="P78" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q78" s="21" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="E37:N37"/>
-    <mergeCell ref="E38:N38"/>
     <mergeCell ref="E31:N31"/>
     <mergeCell ref="E32:N32"/>
     <mergeCell ref="E33:N33"/>
     <mergeCell ref="E34:N34"/>
     <mergeCell ref="E35:N35"/>
     <mergeCell ref="E36:N36"/>
+    <mergeCell ref="E37:N37"/>
+    <mergeCell ref="E38:N38"/>
   </mergeCells>
   <drawing r:id="rId4"/>
   <legacyDrawing r:id="rId5"/>
